--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -20431,23 +20431,19 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H290" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I290" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H290" s="5" t="n">
+        <v>35200000</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>25269</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -20456,12 +20452,12 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
@@ -20471,7 +20467,7 @@
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -24379,7 +24375,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24389,7 +24385,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -24986,12 +24982,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 1393呎 (3房)
-招标单位
--
-(在售)</t>
+$3520万
+$25,269/呎
+(26年-09月-07日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="E288" s="4" t="n">
-        <v>1393</v>
+        <v>1305</v>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
@@ -20300,14 +20300,14 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
         <v>35350000</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>25377</v>
+        <v>27088</v>
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
@@ -24961,10 +24961,10 @@
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 1393呎 (3房)
+          <t>B | 1305呎 (3房)
 $3535万
-$25,377/呎
-(26年-08月-28日)</t>
+$27,088/呎
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -20567,23 +20567,19 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H292" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I292" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H292" s="5" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="I292" s="5" t="n">
+        <v>25126</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
@@ -20592,12 +20588,12 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M292" s="3" t="inlineStr">
@@ -20607,7 +20603,7 @@
       </c>
       <c r="N292" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -24375,7 +24371,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24385,7 +24381,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25005,12 +25001,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 1393呎 (3房)
-招标单位
--
-(在售)</t>
+$3500万
+$25,126/呎
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -20427,7 +20427,7 @@
         </is>
       </c>
       <c r="E290" s="4" t="n">
-        <v>1393</v>
+        <v>1305</v>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
@@ -20436,14 +20436,14 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
         <v>35200000</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>25269</v>
+        <v>26973</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -24980,10 +24980,10 @@
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>B | 1393呎 (3房)
+          <t>B | 1305呎 (3房)
 $3520万
-$25,269/呎
-(26年-09月-07日)</t>
+$26,973/呎
+(26年-10月-08日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -20563,7 +20563,7 @@
         </is>
       </c>
       <c r="E292" s="4" t="n">
-        <v>1393</v>
+        <v>1305</v>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
@@ -20572,14 +20572,14 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
         <v>35000000</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>25126</v>
+        <v>26820</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
@@ -25003,10 +25003,10 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>B | 1393呎 (3房)
+          <t>B | 1305呎 (3房)
 $3500万
-$25,126/呎
-(26年-09月-22日)</t>
+$26,820/呎
+(26年-10月-16日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-鸭脷洲-凯玥.xlsx
+++ b/files/港岛-鸭脷洲-凯玥.xlsx
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>60800000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>32618</v>
+        <v>31084</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2107</v>
+        <v>2247</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>65720256</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>31191</v>
+        <v>29248</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>55253088</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>29642</v>
+        <v>28248</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>59398000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>31866</v>
+        <v>30367</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2107</v>
+        <v>2247</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>69000000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>32748</v>
+        <v>30708</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2107</v>
+        <v>2247</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>66000000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>31324</v>
+        <v>29372</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>54080000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>29013</v>
+        <v>27648</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2107</v>
+        <v>2247</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>67916000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>32234</v>
+        <v>30225</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>58000000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>31116</v>
+        <v>29652</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2107</v>
+        <v>2247</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>66079776</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>31362</v>
+        <v>29408</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>52380000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>28101</v>
+        <v>26779</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2107</v>
+        <v>2247</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         <v>64455620</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>30591</v>
+        <v>28685</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>51834000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>27808</v>
+        <v>26500</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>61886900</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>29358</v>
+        <v>27542</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>55613000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>29835</v>
+        <v>28432</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>62871400</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>29825</v>
+        <v>27980</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>55481480</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>29765</v>
+        <v>28365</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>58646700</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>27821</v>
+        <v>26100</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>50856000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>27283</v>
+        <v>26000</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>58646700</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>27821</v>
+        <v>26100</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>55258200</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>29645</v>
+        <v>28251</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>62972600</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>29873</v>
+        <v>28025</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>55464800</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>29756</v>
+        <v>28356</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>62972600</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>29873</v>
+        <v>28025</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>55464800</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>29756</v>
+        <v>28356</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>64480337</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>30588</v>
+        <v>28696</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>51777276</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>27778</v>
+        <v>26471</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>64545500</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>30619</v>
+        <v>28725</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>49200000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>26395</v>
+        <v>25153</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>60462276</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>28682</v>
+        <v>26908</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>52500000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>28165</v>
+        <v>26840</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2108</v>
+        <v>2247</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>55400000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>26281</v>
+        <v>24655</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1864</v>
+        <v>1956</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>53799800</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>28863</v>
+        <v>27505</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>84939000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>34472</v>
+        <v>32619</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>70939000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>33196</v>
+        <v>31726</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>79942800</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>32444</v>
+        <v>30700</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>82000000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>33279</v>
+        <v>31490</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>65816660</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>30799</v>
+        <v>29435</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>82000000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>33279</v>
+        <v>31490</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>81005232</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>32876</v>
+        <v>31108</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>65264368</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>30540</v>
+        <v>29188</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>81005232</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>32876</v>
+        <v>31108</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>65264368</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>30540</v>
+        <v>29188</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>65264368</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>30540</v>
+        <v>29188</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>83328000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>33818</v>
+        <v>32000</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>81216000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>32961</v>
+        <v>31189</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>80745152</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>32770</v>
+        <v>31008</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>65254848</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>30536</v>
+        <v>29184</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>79000000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>32062</v>
+        <v>30338</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>64780000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>30314</v>
+        <v>28971</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>79000000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>32062</v>
+        <v>30338</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>71632800</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>33520</v>
+        <v>32036</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>81000000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>32873</v>
+        <v>31106</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>78526480</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>31870</v>
+        <v>30156</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>82508060</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>33485</v>
+        <v>31685</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>70962000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>33206</v>
+        <v>31736</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>2464</v>
+        <v>2604</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         <v>78297072</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>31776</v>
+        <v>30068</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>2137</v>
+        <v>2236</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>67232048</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>31461</v>
+        <v>30068</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>3477</v>
+        <v>3627</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>140080000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>40288</v>
+        <v>38621</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>3207</v>
+        <v>3316</v>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>164168000</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>51191</v>
+        <v>49508</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>3477</v>
+        <v>3627</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>172282500</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>49549</v>
+        <v>47500</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>3207</v>
+        <v>3316</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>121060000</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>37749</v>
+        <v>36508</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>3207</v>
+        <v>3316</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>120662608</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>37625</v>
+        <v>36388</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1824</v>
+        <v>1944</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>75816000</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>41566</v>
+        <v>39000</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>2178</v>
+        <v>2310</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>73388000</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>33695</v>
+        <v>31770</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>2178</v>
+        <v>2310</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>67452000</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>30970</v>
+        <v>29200</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>2178</v>
+        <v>2310</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>72506280</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>33290</v>
+        <v>31388</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>1824</v>
+        <v>1944</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>53226720</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>29181</v>
+        <v>27380</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>2178</v>
+        <v>2310</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>69557800</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>31937</v>
+        <v>30112</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>1824</v>
+        <v>1944</v>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>58000000</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>31798</v>
+        <v>29835</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>2178</v>
+        <v>2310</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>64680000</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>29697</v>
+        <v>28000</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>1824</v>
+        <v>1944</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>63180000</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>34638</v>
+        <v>32500</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>2178</v>
+        <v>2310</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>62800000</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>28834</v>
+        <v>27186</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>1824</v>
+        <v>1944</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>57236000</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>31379</v>
+        <v>29442</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>1824</v>
+        <v>1944</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>59525280</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>32634</v>
+        <v>30620</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         </is>
       </c>
       <c r="E187" s="4" t="n">
-        <v>1824</v>
+        <v>1944</v>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>57236000</v>
       </c>
       <c r="I187" s="5" t="n">
-        <v>31379</v>
+        <v>29442</v>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>49100000</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>30197</v>
+        <v>28933</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>47679924</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>29323</v>
+        <v>28097</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>47679924</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>29323</v>
+        <v>28097</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43782600</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>26927</v>
+        <v>25800</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>42056100</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>25977</v>
+        <v>24900</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         </is>
       </c>
       <c r="E217" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>42425000</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>26092</v>
+        <v>25000</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>41887200</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>25872</v>
+        <v>24800</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         </is>
       </c>
       <c r="E219" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>42085600</v>
       </c>
       <c r="I219" s="5" t="n">
-        <v>25883</v>
+        <v>24800</v>
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45042700</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>27821</v>
+        <v>26668</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         </is>
       </c>
       <c r="E221" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>41237100</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>25361</v>
+        <v>24300</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>41718300</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>25768</v>
+        <v>24700</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>45915900</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>28239</v>
+        <v>27057</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         </is>
       </c>
       <c r="E224" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>41550000</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>25664</v>
+        <v>24600</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>41576500</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>25570</v>
+        <v>24500</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>42380000</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>26177</v>
+        <v>25092</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         </is>
       </c>
       <c r="E227" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>42000000</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>25830</v>
+        <v>24750</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         </is>
       </c>
       <c r="E228" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>42000000</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>25942</v>
+        <v>24867</v>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>41576500</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>25570</v>
+        <v>24500</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>43162395</v>
       </c>
       <c r="I230" s="5" t="n">
-        <v>26660</v>
+        <v>25555</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>41406800</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>25465</v>
+        <v>24400</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="E232" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>41500000</v>
       </c>
       <c r="I232" s="5" t="n">
-        <v>25633</v>
+        <v>24571</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45228000</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>27815</v>
+        <v>26652</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>47500195</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>29339</v>
+        <v>28123</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>41627410</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>25601</v>
+        <v>24530</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>42731700</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>26394</v>
+        <v>25300</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>42085600</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>25883</v>
+        <v>24800</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>1619</v>
+        <v>1689</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>49500000</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>30574</v>
+        <v>29307</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>1626</v>
+        <v>1697</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>43273500</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>26613</v>
+        <v>25500</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         </is>
       </c>
       <c r="E286" s="4" t="n">
-        <v>1305</v>
+        <v>1393</v>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>36000000</v>
       </c>
       <c r="I286" s="5" t="n">
-        <v>27586</v>
+        <v>25844</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         </is>
       </c>
       <c r="E288" s="4" t="n">
-        <v>1305</v>
+        <v>1393</v>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>35350000</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>27088</v>
+        <v>25377</v>
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         </is>
       </c>
       <c r="E290" s="4" t="n">
-        <v>1305</v>
+        <v>1393</v>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>35200000</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>26973</v>
+        <v>25269</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         </is>
       </c>
       <c r="E292" s="4" t="n">
-        <v>1305</v>
+        <v>1393</v>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>35000000</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>26820</v>
+        <v>25126</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
@@ -21177,9 +21177,9 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $6080万
-$32,618/呎
+$31,084/呎
 (25年-09月-02日)</t>
         </is>
       </c>
@@ -21200,17 +21200,17 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5525万
-$29,642/呎
+$28,248/呎
 (25年-09月-16日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>B | 2107呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6572万
-$31,191/呎
+$29,248/呎
 (25年-09月-11日)</t>
         </is>
       </c>
@@ -21223,9 +21223,9 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5940万
-$31,866/呎
+$30,367/呎
 (25年-07月-11日)</t>
         </is>
       </c>
@@ -21254,9 +21254,9 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>B | 2107呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6900万
-$32,748/呎
+$30,708/呎
 (24年-08月-21日)</t>
         </is>
       </c>
@@ -21269,17 +21269,17 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5408万
-$29,013/呎
+$27,648/呎
 (25年-07月-11日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>B | 2107呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6600万
-$31,324/呎
+$29,372/呎
 (24年-10月-16日)</t>
         </is>
       </c>
@@ -21292,17 +21292,17 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5800万
-$31,116/呎
+$29,652/呎
 (24年-11月-15日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>B | 2107呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6792万
-$32,234/呎
+$30,225/呎
 (25年-07月-15日)</t>
         </is>
       </c>
@@ -21315,17 +21315,17 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5238万
-$28,101/呎
+$26,779/呎
 (24年-10月-16日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>B | 2107呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6608万
-$31,362/呎
+$29,408/呎
 (24年-09月-10日)</t>
         </is>
       </c>
@@ -21338,17 +21338,17 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5183万
-$27,808/呎
+$26,500/呎
 (24年-07月-17日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>B | 2107呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6446万
-$30,591/呎
+$28,685/呎
 (24年-07月-12日)</t>
         </is>
       </c>
@@ -21361,17 +21361,17 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5561万
-$29,835/呎
+$28,432/呎
 (24年-06月-12日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6189万
-$29,358/呎
+$27,542/呎
 (24年-07月-04日)</t>
         </is>
       </c>
@@ -21384,17 +21384,17 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5548万
-$29,765/呎
+$28,365/呎
 (24年-05月-16日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6287万
-$29,825/呎
+$27,980/呎
 (24年-05月-17日)</t>
         </is>
       </c>
@@ -21407,17 +21407,17 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5086万
-$27,283/呎
+$26,000/呎
 (24年-05月-16日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $5865万
-$27,821/呎
+$26,100/呎
 (24年-05月-17日)</t>
         </is>
       </c>
@@ -21430,17 +21430,17 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5526万
-$29,645/呎
+$28,251/呎
 (24年-05月-21日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $5865万
-$27,821/呎
+$26,100/呎
 (24年-05月-17日)</t>
         </is>
       </c>
@@ -21453,17 +21453,17 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5546万
-$29,756/呎
+$28,356/呎
 (24年-05月-16日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6297万
-$29,873/呎
+$28,025/呎
 (24年-05月-16日)</t>
         </is>
       </c>
@@ -21476,17 +21476,17 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5546万
-$29,756/呎
+$28,356/呎
 (24年-05月-16日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6297万
-$29,873/呎
+$28,025/呎
 (24年-05月-16日)</t>
         </is>
       </c>
@@ -21499,17 +21499,17 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5178万
-$27,778/呎
+$26,471/呎
 (24年-05月-17日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6448万
-$30,588/呎
+$28,696/呎
 (24年-05月-17日)</t>
         </is>
       </c>
@@ -21522,17 +21522,17 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $4920万
-$26,395/呎
+$25,153/呎
 (24年-07月-12日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6455万
-$30,619/呎
+$28,725/呎
 (24年-05月-16日)</t>
         </is>
       </c>
@@ -21545,17 +21545,17 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5250万
-$28,165/呎
+$26,840/呎
 (25年-02月-20日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $6046万
-$28,682/呎
+$26,908/呎
 (24年-09月-25日)</t>
         </is>
       </c>
@@ -21568,17 +21568,17 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 1864呎 (4+房)
+          <t>A | 1956呎 (4+房)
 $5380万
-$28,863/呎
+$27,505/呎
 (26年-01月-29日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 2108呎 (4+房)
+          <t>B | 2247呎 (4+房)
 $5540万
-$26,281/呎
+$24,655/呎
 (25年-01月-13日)</t>
         </is>
       </c>
@@ -21872,17 +21872,17 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>A | 2137呎 (4+房)
+          <t>A | 2236呎 (4+房)
 $7094万
-$33,196/呎
+$31,726/呎
 (25年-10月-23日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $8494万
-$34,472/呎
+$32,619/呎
 (25年-10月-23日)</t>
         </is>
       </c>
@@ -21903,9 +21903,9 @@
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $7994万
-$32,444/呎
+$30,700/呎
 (25年-10月-16日)</t>
         </is>
       </c>
@@ -21918,17 +21918,17 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>A | 2137呎 (4+房)
+          <t>A | 2236呎 (4+房)
 $6582万
-$30,799/呎
+$29,435/呎
 (25年-10月-22日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $8200万
-$33,279/呎
+$31,490/呎
 (25年-08月-04日)</t>
         </is>
       </c>
@@ -21949,9 +21949,9 @@
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $8200万
-$33,279/呎
+$31,490/呎
 (25年-08月-04日)</t>
         </is>
       </c>
@@ -21964,59 +21964,13 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>A | 2137呎 (4+房)
+          <t>A | 2236呎 (4+房)
 $6526万
-$30,540/呎
+$29,188/呎
 (25年-04月-17日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8101万
-$32,876/呎
-(25年-04月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$6526万
-$30,540/呎
-(25年-04月-17日)</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>B | 2464呎 (4+房)
-$8101万
-$32,876/呎
-(25年-04月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>A | 2137呎 (4+房)
-$6526万
-$30,540/呎
-(25年-04月-17日)</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 2604呎 (4+房)
 $8101万
@@ -22025,6 +21979,52 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+$6526万
+$29,188/呎
+(25年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 2604呎 (4+房)
+$8101万
+$31,108/呎
+(25年-04月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 2236呎 (4+房)
+$6526万
+$29,188/呎
+(25年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 2604呎 (4+房)
+$8101万
+$31,108/呎
+(25年-04月-17日)</t>
+        </is>
+      </c>
+    </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
@@ -22041,9 +22041,9 @@
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $8333万
-$33,818/呎
+$32,000/呎
 (25年-01月-22日)</t>
         </is>
       </c>
@@ -22064,9 +22064,9 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $8122万
-$32,961/呎
+$31,189/呎
 (25年-05月-23日)</t>
         </is>
       </c>
@@ -22079,17 +22079,17 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 2137呎 (4+房)
+          <t>A | 2236呎 (4+房)
 $6525万
-$30,536/呎
+$29,184/呎
 (25年-02月-17日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $8075万
-$32,770/呎
+$31,008/呎
 (25年-02月-18日)</t>
         </is>
       </c>
@@ -22102,17 +22102,17 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 2137呎 (4+房)
+          <t>A | 2236呎 (4+房)
 $6478万
-$30,314/呎
+$28,971/呎
 (25年-09月-30日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $7900万
-$32,062/呎
+$30,338/呎
 (24年-12月-04日)</t>
         </is>
       </c>
@@ -22125,17 +22125,17 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 2137呎 (4+房)
+          <t>A | 2236呎 (4+房)
 $7163万
-$33,520/呎
+$32,036/呎
 (25年-12月-19日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $7900万
-$32,062/呎
+$30,338/呎
 (24年-12月-04日)</t>
         </is>
       </c>
@@ -22156,9 +22156,9 @@
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $8100万
-$32,873/呎
+$31,106/呎
 (25年-06月-03日)</t>
         </is>
       </c>
@@ -22179,9 +22179,9 @@
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $7853万
-$31,870/呎
+$30,156/呎
 (25年-01月-15日)</t>
         </is>
       </c>
@@ -22194,17 +22194,17 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 2137呎 (4+房)
+          <t>A | 2236呎 (4+房)
 $7096万
-$33,206/呎
+$31,736/呎
 (25年-12月-19日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $8251万
-$33,485/呎
+$31,685/呎
 (25年-12月-19日)</t>
         </is>
       </c>
@@ -22217,17 +22217,17 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 2137呎 (4+房)
+          <t>A | 2236呎 (4+房)
 $6723万
-$31,461/呎
+$30,068/呎
 (26年-06月-03日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 2464呎 (4+房)
+          <t>B | 2604呎 (4+房)
 $7830万
-$31,776/呎
+$30,068/呎
 (26年-06月-03日)</t>
         </is>
       </c>
@@ -22751,17 +22751,17 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 3207呎 (4+房)
+          <t>A | 3316呎 (4+房)
 $16417万
-$51,191/呎
+$49,508/呎
 (23年-01月-27日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 3477呎 (4+房)
+          <t>B | 3627呎 (4+房)
 $14008万
-$40,288/呎
+$38,621/呎
 (26年-05月-04日)</t>
         </is>
       </c>
@@ -22782,9 +22782,9 @@
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 3477呎 (4+房)
+          <t>B | 3627呎 (4+房)
 $17228万
-$49,549/呎
+$47,500/呎
 (23年-12月-15日)</t>
         </is>
       </c>
@@ -22797,9 +22797,9 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 3207呎 (4+房)
+          <t>A | 3316呎 (4+房)
 $12106万
-$37,749/呎
+$36,508/呎
 (24年-07月-18日)</t>
         </is>
       </c>
@@ -22843,9 +22843,9 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 3207呎 (4+房)
+          <t>A | 3316呎 (4+房)
 $12066万
-$37,625/呎
+$36,388/呎
 (26年-04月-24日)</t>
         </is>
       </c>
@@ -23201,9 +23201,9 @@
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>B | 1824呎 (4+房)
+          <t>B | 1944呎 (4+房)
 $7582万
-$41,566/呎
+$39,000/呎
 (24年-01月-22日)</t>
         </is>
       </c>
@@ -23354,9 +23354,9 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 2178呎 (4+房)
+          <t>A | 2310呎 (4+房)
 $7339万
-$33,695/呎
+$31,770/呎
 (25年-10月-09日)</t>
         </is>
       </c>
@@ -23400,9 +23400,9 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 2178呎 (4+房)
+          <t>A | 2310呎 (4+房)
 $6745万
-$30,970/呎
+$29,200/呎
 (25年-08月-12日)</t>
         </is>
       </c>
@@ -23423,9 +23423,9 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 2178呎 (4+房)
+          <t>A | 2310呎 (4+房)
 $7251万
-$33,290/呎
+$31,388/呎
 (24年-11月-04日)</t>
         </is>
       </c>
@@ -23446,17 +23446,17 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 2178呎 (4+房)
+          <t>A | 2310呎 (4+房)
 $6956万
-$31,937/呎
+$30,112/呎
 (25年-10月-02日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 1824呎 (4+房)
+          <t>B | 1944呎 (4+房)
 $5323万
-$29,181/呎
+$27,380/呎
 (25年-10月-02日)</t>
         </is>
       </c>
@@ -23469,17 +23469,17 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 2178呎 (4+房)
+          <t>A | 2310呎 (4+房)
 $6468万
-$29,697/呎
+$28,000/呎
 (24年-07月-04日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 1824呎 (4+房)
+          <t>B | 1944呎 (4+房)
 $5800万
-$31,798/呎
+$29,835/呎
 (24年-05月-17日)</t>
         </is>
       </c>
@@ -23492,17 +23492,17 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>A | 2178呎 (4+房)
+          <t>A | 2310呎 (4+房)
 $6280万
-$28,834/呎
+$27,186/呎
 (25年-07月-29日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 1824呎 (4+房)
+          <t>B | 1944呎 (4+房)
 $6318万
-$34,638/呎
+$32,500/呎
 (26年-08月-11日)</t>
         </is>
       </c>
@@ -23523,9 +23523,9 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 1824呎 (4+房)
+          <t>B | 1944呎 (4+房)
 $5724万
-$31,379/呎
+$29,442/呎
 (26年-02月-02日)</t>
         </is>
       </c>
@@ -23546,9 +23546,9 @@
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 1824呎 (4+房)
+          <t>B | 1944呎 (4+房)
 $5953万
-$32,634/呎
+$30,620/呎
 (26年-06月-24日)</t>
         </is>
       </c>
@@ -23569,9 +23569,9 @@
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 1824呎 (4+房)
+          <t>B | 1944呎 (4+房)
 $5724万
-$31,379/呎
+$29,442/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -23895,9 +23895,9 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4910万
-$30,197/呎
+$28,933/呎
 (25年-09月-15日)</t>
         </is>
       </c>
@@ -23918,9 +23918,9 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4768万
-$29,323/呎
+$28,097/呎
 (25年-05月-29日)</t>
         </is>
       </c>
@@ -23941,9 +23941,9 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4768万
-$29,323/呎
+$28,097/呎
 (25年-06月-02日)</t>
         </is>
       </c>
@@ -23964,9 +23964,9 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4378万
-$26,927/呎
+$25,800/呎
 (25年-06月-19日)</t>
         </is>
       </c>
@@ -24010,17 +24010,17 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4242万
-$26,092/呎
+$25,000/呎
 (25年-05月-15日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4206万
-$25,977/呎
+$24,900/呎
 (25年-07月-02日)</t>
         </is>
       </c>
@@ -24033,17 +24033,17 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4209万
-$25,883/呎
+$24,800/呎
 (25年-05月-08日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4189万
-$25,872/呎
+$24,800/呎
 (25年-06月-03日)</t>
         </is>
       </c>
@@ -24056,17 +24056,17 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4124万
-$25,361/呎
+$24,300/呎
 (24年-06月-28日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4504万
-$27,821/呎
+$26,668/呎
 (24年-06月-28日)</t>
         </is>
       </c>
@@ -24079,17 +24079,17 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4592万
-$28,239/呎
+$27,057/呎
 (24年-11月-07日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4172万
-$25,768/呎
+$24,700/呎
 (25年-02月-19日)</t>
         </is>
       </c>
@@ -24102,17 +24102,17 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4158万
-$25,570/呎
+$24,500/呎
 (24年-10月-31日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4155万
-$25,664/呎
+$24,600/呎
 (24年-11月-11日)</t>
         </is>
       </c>
@@ -24125,17 +24125,17 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4200万
-$25,830/呎
+$24,750/呎
 (24年-12月-18日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4238万
-$26,177/呎
+$25,092/呎
 (25年-10月-03日)</t>
         </is>
       </c>
@@ -24148,17 +24148,17 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4158万
-$25,570/呎
+$24,500/呎
 (24年-11月-22日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4200万
-$25,942/呎
+$24,867/呎
 (25年-10月-06日)</t>
         </is>
       </c>
@@ -24171,17 +24171,17 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4141万
-$25,465/呎
+$24,400/呎
 (24年-07月-17日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4316万
-$26,660/呎
+$25,555/呎
 (25年-12月-04日)</t>
         </is>
       </c>
@@ -24194,17 +24194,17 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4523万
-$27,815/呎
+$26,652/呎
 (24年-10月-31日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4150万
-$25,633/呎
+$24,571/呎
 (25年-10月-30日)</t>
         </is>
       </c>
@@ -24217,17 +24217,17 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4163万
-$25,601/呎
+$24,530/呎
 (25年-07月-02日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4750万
-$29,339/呎
+$28,123/呎
 (25年-12月-11日)</t>
         </is>
       </c>
@@ -24240,17 +24240,17 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4209万
-$25,883/呎
+$24,800/呎
 (25年-05月-30日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4273万
-$26,394/呎
+$25,300/呎
 (25年-12月-18日)</t>
         </is>
       </c>
@@ -24263,17 +24263,17 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>A | 1626呎 (4+房)
+          <t>A | 1697呎 (4+房)
 $4327万
-$26,613/呎
+$25,500/呎
 (25年-12月-11日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>B | 1619呎 (4+房)
+          <t>B | 1689呎 (4+房)
 $4950万
-$30,574/呎
+$29,307/呎
 (26年-02月-10日)</t>
         </is>
       </c>
@@ -24934,9 +24934,9 @@
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>B | 1305呎 (3房)
+          <t>B | 1393呎 (3房)
 $3600万
-$27,586/呎
+$25,844/呎
 (26年-09月-02日)</t>
         </is>
       </c>
@@ -24957,9 +24957,9 @@
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>B | 1305呎 (3房)
+          <t>B | 1393呎 (3房)
 $3535万
-$27,088/呎
+$25,377/呎
 (26年-09月-16日)</t>
         </is>
       </c>
@@ -24980,9 +24980,9 @@
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>B | 1305呎 (3房)
+          <t>B | 1393呎 (3房)
 $3520万
-$26,973/呎
+$25,269/呎
 (26年-10月-08日)</t>
         </is>
       </c>
@@ -25003,9 +25003,9 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>B | 1305呎 (3房)
+          <t>B | 1393呎 (3房)
 $3500万
-$26,820/呎
+$25,126/呎
 (26年-10月-16日)</t>
         </is>
       </c>
